--- a/Result/profitability/6133.xlsx
+++ b/Result/profitability/6133.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1825</v>
+        <v>0.21875</v>
       </c>
       <c r="N2" t="n">
-        <v>22.62375</v>
+        <v>23.34375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2125</v>
+        <v>0.23375</v>
       </c>
       <c r="N3" t="n">
-        <v>22.32375</v>
+        <v>23.565</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.175</v>
+        <v>0.20625</v>
       </c>
       <c r="N4" t="n">
-        <v>21.895</v>
+        <v>22.6125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1375</v>
+        <v>0.18375</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6</v>
+        <v>20.285</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12375</v>
+        <v>0.14</v>
       </c>
       <c r="N6" t="n">
-        <v>17.78625</v>
+        <v>17.82125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0.09874999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>15.895</v>
+        <v>15.92625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.055</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>15.895</v>
+        <v>16.2425</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -9828,6 +9828,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>370</v>
+      </c>
+      <c r="D75" t="n">
+        <v>271</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>53</v>
+      </c>
+      <c r="K75" t="n">
+        <v>43</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.9725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.846153846153846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1159783062161035</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2576398683591914</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
